--- a/lab4/checkpoint1.xlsx
+++ b/lab4/checkpoint1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\faisaln\RPI-CS-1200\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8EABAC-625C-479E-8CA5-2F902E622E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4867F36B-196B-4A1E-93B0-0A9BD3FD31F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="264" yWindow="600" windowWidth="22512" windowHeight="13476" xr2:uid="{BDB2C7E4-5971-487F-B5C1-250D97847A57}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>Stack</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Point* q</t>
   </si>
   <si>
-    <t>Point 0x555</t>
-  </si>
-  <si>
     <t>int r-&gt;x = ?</t>
   </si>
   <si>
@@ -108,6 +105,9 @@
   </si>
   <si>
     <t>int* arr</t>
+  </si>
+  <si>
+    <t>Point 0x___</t>
   </si>
 </sst>
 </file>
@@ -158,15 +158,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1160,19 +1157,19 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>304720</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>10080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>305440</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>51120</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="15" name="Ink 14">
@@ -1191,7 +1188,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="15" name="Ink 14">
@@ -1225,19 +1222,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>187720</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>127080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>465640</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>60840</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="18" name="Ink 17">
@@ -1256,7 +1253,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="18" name="Ink 17">
@@ -1534,7 +1531,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24245,'0'7733'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24245,'0'7777'0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -2130,20 +2127,20 @@
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -2154,7 +2151,7 @@
         <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
@@ -2162,15 +2159,15 @@
         <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -2178,21 +2175,20 @@
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
@@ -2208,17 +2204,20 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C18" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="E18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
